--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14102,6 +14102,218 @@
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128778236</v>
+      </c>
+      <c r="B128" t="n">
+        <v>78449</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>498</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>415431</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7041021</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>Luckig och gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128784733</v>
+      </c>
+      <c r="B129" t="n">
+        <v>92774</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Finndalen, Finndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>415450</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7040750</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78449</v>
+        <v>78476</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14314,6 +14314,112 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128928885</v>
+      </c>
+      <c r="B130" t="n">
+        <v>90934</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Finndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>415389</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7040827</v>
+      </c>
+      <c r="S130" t="n">
+        <v>25</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78480</v>
+        <v>78484</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90934</v>
+        <v>90938</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78484</v>
+        <v>78389</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90938</v>
+        <v>90943</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90950</v>
+        <v>90953</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78394</v>
+        <v>78395</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90953</v>
+        <v>90956</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78395</v>
+        <v>78399</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90956</v>
+        <v>90960</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90960</v>
+        <v>90967</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14107,7 +14107,7 @@
         <v>128778236</v>
       </c>
       <c r="B128" t="n">
-        <v>78399</v>
+        <v>78401</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90967</v>
+        <v>90969</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14213,7 +14213,7 @@
         <v>128784733</v>
       </c>
       <c r="B129" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -14319,7 +14319,7 @@
         <v>128928885</v>
       </c>
       <c r="B130" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY130"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112713042</v>
+        <v>128778236</v>
       </c>
       <c r="B2" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>sölvsved, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415341</v>
+        <v>415431</v>
       </c>
       <c r="R2" t="n">
-        <v>7040870</v>
+        <v>7041021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +757,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Luckig och gammal grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112712994</v>
+        <v>112713036</v>
       </c>
       <c r="B3" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415350</v>
+        <v>415390</v>
       </c>
       <c r="R3" t="n">
-        <v>7040859</v>
+        <v>7040817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112712958</v>
+        <v>112713037</v>
       </c>
       <c r="B4" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415423</v>
+        <v>415451</v>
       </c>
       <c r="R4" t="n">
-        <v>7040962</v>
+        <v>7040768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112712925</v>
+        <v>112713038</v>
       </c>
       <c r="B5" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415253</v>
+        <v>415301</v>
       </c>
       <c r="R5" t="n">
-        <v>7040590</v>
+        <v>7040859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112712992</v>
+        <v>112712888</v>
       </c>
       <c r="B6" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415269</v>
+        <v>415277</v>
       </c>
       <c r="R6" t="n">
-        <v>7040917</v>
+        <v>7040685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1143,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112712965</v>
+        <v>112712889</v>
       </c>
       <c r="B7" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415389</v>
+        <v>415347</v>
       </c>
       <c r="R7" t="n">
-        <v>7041217</v>
+        <v>7040725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1240,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,37 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112713007</v>
+        <v>112712890</v>
       </c>
       <c r="B8" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>415289</v>
+        <v>415410</v>
       </c>
       <c r="R8" t="n">
-        <v>7040820</v>
+        <v>7040794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1337,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,37 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112712979</v>
+        <v>112712891</v>
       </c>
       <c r="B9" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>415288</v>
+        <v>415185</v>
       </c>
       <c r="R9" t="n">
-        <v>7040981</v>
+        <v>7040631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1434,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,53 +1460,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112713011</v>
+        <v>128928885</v>
       </c>
       <c r="B10" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4189</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sölvsved, Jmt</t>
+          <t>Finndalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>415297</v>
+        <v>415389</v>
       </c>
       <c r="R10" t="n">
-        <v>7040818</v>
+        <v>7040827</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,17 +1528,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,33 +1542,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i grannaturskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112712983</v>
+        <v>128784733</v>
       </c>
       <c r="B11" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1577,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>sölvsved, Jmt</t>
+          <t>Finndalen, Finndalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>415233</v>
+        <v>415450</v>
       </c>
       <c r="R11" t="n">
-        <v>7040952</v>
+        <v>7040750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,17 +1634,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,55 +1648,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrikt bäckdråg i grannaturskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112712930</v>
+        <v>112713043</v>
       </c>
       <c r="B12" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>415270</v>
+        <v>415238</v>
       </c>
       <c r="R12" t="n">
-        <v>7040639</v>
+        <v>7040689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1743,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,15 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112713006</v>
+        <v>112712902</v>
       </c>
       <c r="B13" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>415272</v>
+        <v>415265</v>
       </c>
       <c r="R13" t="n">
-        <v>7040821</v>
+        <v>7040565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1844,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,15 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112712996</v>
+        <v>112712903</v>
       </c>
       <c r="B14" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>415347</v>
+        <v>415308</v>
       </c>
       <c r="R14" t="n">
-        <v>7040858</v>
+        <v>7040597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +1946,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,15 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112712954</v>
+        <v>112712904</v>
       </c>
       <c r="B15" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>415435</v>
+        <v>415339</v>
       </c>
       <c r="R15" t="n">
-        <v>7040892</v>
+        <v>7040651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2048,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,15 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112712971</v>
+        <v>112712905</v>
       </c>
       <c r="B16" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>415297</v>
+        <v>415350</v>
       </c>
       <c r="R16" t="n">
-        <v>7041071</v>
+        <v>7040668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,15 +2177,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112713017</v>
+        <v>112712906</v>
       </c>
       <c r="B17" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2212,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>415261</v>
+        <v>415363</v>
       </c>
       <c r="R17" t="n">
-        <v>7040775</v>
+        <v>7040678</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2252,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,15 +2279,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112712933</v>
+        <v>112712907</v>
       </c>
       <c r="B18" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2314,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>415305</v>
+        <v>415392</v>
       </c>
       <c r="R18" t="n">
-        <v>7040729</v>
+        <v>7040698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,15 +2381,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112712917</v>
+        <v>112712908</v>
       </c>
       <c r="B19" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,10 +2416,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>415356</v>
+        <v>415404</v>
       </c>
       <c r="R19" t="n">
-        <v>7040677</v>
+        <v>7040705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,15 +2483,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112713008</v>
+        <v>112712909</v>
       </c>
       <c r="B20" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>415294</v>
+        <v>415405</v>
       </c>
       <c r="R20" t="n">
-        <v>7040823</v>
+        <v>7040719</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,15 +2585,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112712918</v>
+        <v>112712911</v>
       </c>
       <c r="B21" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2620,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>415308</v>
+        <v>415403</v>
       </c>
       <c r="R21" t="n">
-        <v>7040629</v>
+        <v>7040719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,15 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112713014</v>
+        <v>112712912</v>
       </c>
       <c r="B22" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2722,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>415288</v>
+        <v>415413</v>
       </c>
       <c r="R22" t="n">
-        <v>7040757</v>
+        <v>7040721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2762,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,15 +2789,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112713000</v>
+        <v>112712913</v>
       </c>
       <c r="B23" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2824,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>415304</v>
+        <v>415415</v>
       </c>
       <c r="R23" t="n">
-        <v>7040832</v>
+        <v>7040728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,15 +2891,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112712913</v>
+        <v>112712914</v>
       </c>
       <c r="B24" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,10 +2926,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>415415</v>
+        <v>415434</v>
       </c>
       <c r="R24" t="n">
-        <v>7040728</v>
+        <v>7040729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,15 +2993,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112712908</v>
+        <v>112712915</v>
       </c>
       <c r="B25" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,10 +3028,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>415404</v>
+        <v>415395</v>
       </c>
       <c r="R25" t="n">
-        <v>7040705</v>
+        <v>7040748</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,15 +3095,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112713003</v>
+        <v>112712916</v>
       </c>
       <c r="B26" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>415316</v>
+        <v>415377</v>
       </c>
       <c r="R26" t="n">
-        <v>7040849</v>
+        <v>7040744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,15 +3197,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112712915</v>
+        <v>112712917</v>
       </c>
       <c r="B27" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3232,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>415395</v>
+        <v>415356</v>
       </c>
       <c r="R27" t="n">
-        <v>7040748</v>
+        <v>7040678</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,15 +3299,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112713013</v>
+        <v>112712918</v>
       </c>
       <c r="B28" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3492,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>415292</v>
+        <v>415308</v>
       </c>
       <c r="R28" t="n">
-        <v>7040773</v>
+        <v>7040629</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3374,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,15 +3401,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112713026</v>
+        <v>112712919</v>
       </c>
       <c r="B29" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,10 +3436,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>415227</v>
+        <v>415311</v>
       </c>
       <c r="R29" t="n">
-        <v>7040661</v>
+        <v>7040609</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,15 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112713038</v>
+        <v>112712920</v>
       </c>
       <c r="B30" t="n">
-        <v>89792</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3538,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>415301</v>
+        <v>415299</v>
       </c>
       <c r="R30" t="n">
-        <v>7040859</v>
+        <v>7040617</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,6 +3574,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,15 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112712969</v>
+        <v>112712923</v>
       </c>
       <c r="B31" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>415338</v>
+        <v>415291</v>
       </c>
       <c r="R31" t="n">
-        <v>7041194</v>
+        <v>7040612</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3680,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,15 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112712937</v>
+        <v>112712925</v>
       </c>
       <c r="B32" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>415333</v>
+        <v>415253</v>
       </c>
       <c r="R32" t="n">
-        <v>7040741</v>
+        <v>7040590</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3782,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,15 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112712906</v>
+        <v>112712926</v>
       </c>
       <c r="B33" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>415363</v>
+        <v>415249</v>
       </c>
       <c r="R33" t="n">
-        <v>7040679</v>
+        <v>7040597</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,15 +3911,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112712963</v>
+        <v>112712927</v>
       </c>
       <c r="B34" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4129,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>415399</v>
+        <v>415246</v>
       </c>
       <c r="R34" t="n">
-        <v>7041070</v>
+        <v>7040589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +3986,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4196,15 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112713029</v>
+        <v>112712928</v>
       </c>
       <c r="B35" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>415190</v>
+        <v>415239</v>
       </c>
       <c r="R35" t="n">
-        <v>7040634</v>
+        <v>7040591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4088,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,15 +4115,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112712972</v>
+        <v>112712929</v>
       </c>
       <c r="B36" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,10 +4150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>415293</v>
+        <v>415236</v>
       </c>
       <c r="R36" t="n">
-        <v>7041026</v>
+        <v>7040613</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4190,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,15 +4217,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112712909</v>
+        <v>112712930</v>
       </c>
       <c r="B37" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,10 +4252,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>415404</v>
+        <v>415270</v>
       </c>
       <c r="R37" t="n">
-        <v>7040719</v>
+        <v>7040638</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4517,15 +4319,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112712916</v>
+        <v>112712931</v>
       </c>
       <c r="B38" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,10 +4354,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>415377</v>
+        <v>415275</v>
       </c>
       <c r="R38" t="n">
-        <v>7040743</v>
+        <v>7040650</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4394,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,15 +4421,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112713020</v>
+        <v>112712932</v>
       </c>
       <c r="B39" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,10 +4456,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>415253</v>
+        <v>415277</v>
       </c>
       <c r="R39" t="n">
-        <v>7040767</v>
+        <v>7040711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4496,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,15 +4523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112713040</v>
+        <v>112712933</v>
       </c>
       <c r="B40" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4747,21 +4534,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4771,10 +4558,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>415209</v>
+        <v>415306</v>
       </c>
       <c r="R40" t="n">
-        <v>7040586</v>
+        <v>7040729</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,6 +4594,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,15 +4625,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112713041</v>
+        <v>112712934</v>
       </c>
       <c r="B41" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4636,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4660,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>415416</v>
+        <v>415330</v>
       </c>
       <c r="R41" t="n">
-        <v>7041171</v>
+        <v>7040715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4909,6 +4696,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4935,15 +4727,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112713027</v>
+        <v>112712935</v>
       </c>
       <c r="B42" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,10 +4762,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>415223</v>
+        <v>415343</v>
       </c>
       <c r="R42" t="n">
-        <v>7040638</v>
+        <v>7040734</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +4802,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5042,15 +4829,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112712914</v>
+        <v>112712936</v>
       </c>
       <c r="B43" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,10 +4864,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>415433</v>
+        <v>415339</v>
       </c>
       <c r="R43" t="n">
-        <v>7040729</v>
+        <v>7040732</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +4904,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5149,15 +4931,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112712959</v>
+        <v>112712937</v>
       </c>
       <c r="B44" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,10 +4966,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>415435</v>
+        <v>415334</v>
       </c>
       <c r="R44" t="n">
-        <v>7040972</v>
+        <v>7040741</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5006,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5256,15 +5033,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112712943</v>
+        <v>112712938</v>
       </c>
       <c r="B45" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5296,10 +5068,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>415464</v>
+        <v>415338</v>
       </c>
       <c r="R45" t="n">
-        <v>7040788</v>
+        <v>7040781</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5363,15 +5135,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112713016</v>
+        <v>112712939</v>
       </c>
       <c r="B46" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5403,10 +5170,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>415271</v>
+        <v>415332</v>
       </c>
       <c r="R46" t="n">
-        <v>7040773</v>
+        <v>7040815</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5210,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5470,15 +5237,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112712956</v>
+        <v>112712941</v>
       </c>
       <c r="B47" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5510,10 +5272,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>415378</v>
+        <v>415333</v>
       </c>
       <c r="R47" t="n">
-        <v>7040937</v>
+        <v>7040824</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5550,7 +5312,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5577,15 +5339,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112713022</v>
+        <v>112712942</v>
       </c>
       <c r="B48" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5617,10 +5374,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>415181</v>
+        <v>415413</v>
       </c>
       <c r="R48" t="n">
-        <v>7040755</v>
+        <v>7040797</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,7 +5414,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5684,15 +5441,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112712944</v>
+        <v>112712943</v>
       </c>
       <c r="B49" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5724,10 +5476,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>415455</v>
+        <v>415464</v>
       </c>
       <c r="R49" t="n">
-        <v>7040854</v>
+        <v>7040788</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5791,15 +5543,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112713005</v>
+        <v>112712944</v>
       </c>
       <c r="B50" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5831,10 +5578,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>415266</v>
+        <v>415455</v>
       </c>
       <c r="R50" t="n">
-        <v>7040832</v>
+        <v>7040854</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5898,15 +5645,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112713037</v>
+        <v>112712945</v>
       </c>
       <c r="B51" t="n">
-        <v>89792</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5914,21 +5656,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5938,10 +5680,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>415451</v>
+        <v>415466</v>
       </c>
       <c r="R51" t="n">
-        <v>7040767</v>
+        <v>7040854</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5974,6 +5716,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6000,15 +5747,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112713019</v>
+        <v>112712946</v>
       </c>
       <c r="B52" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6040,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>415256</v>
+        <v>415388</v>
       </c>
       <c r="R52" t="n">
-        <v>7040761</v>
+        <v>7040852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6080,7 +5822,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6107,15 +5849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112712911</v>
+        <v>112712947</v>
       </c>
       <c r="B53" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6147,10 +5884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>415403</v>
+        <v>415381</v>
       </c>
       <c r="R53" t="n">
-        <v>7040719</v>
+        <v>7040856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,7 +5924,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6214,15 +5951,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112712928</v>
+        <v>112712948</v>
       </c>
       <c r="B54" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6254,10 +5986,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>415239</v>
+        <v>415387</v>
       </c>
       <c r="R54" t="n">
-        <v>7040591</v>
+        <v>7040874</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6294,7 +6026,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6321,15 +6053,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112712985</v>
+        <v>112712949</v>
       </c>
       <c r="B55" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6361,10 +6088,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>415236</v>
+        <v>415364</v>
       </c>
       <c r="R55" t="n">
-        <v>7040943</v>
+        <v>7040888</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6401,7 +6128,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6428,15 +6155,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112712948</v>
+        <v>112712950</v>
       </c>
       <c r="B56" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,10 +6190,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>415387</v>
+        <v>415356</v>
       </c>
       <c r="R56" t="n">
-        <v>7040874</v>
+        <v>7040897</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6535,15 +6257,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112712987</v>
+        <v>112712951</v>
       </c>
       <c r="B57" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6575,10 +6292,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>415263</v>
+        <v>415371</v>
       </c>
       <c r="R57" t="n">
-        <v>7040926</v>
+        <v>7040907</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6615,7 +6332,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6642,15 +6359,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112712951</v>
+        <v>112712952</v>
       </c>
       <c r="B58" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6682,10 +6394,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>415371</v>
+        <v>415380</v>
       </c>
       <c r="R58" t="n">
-        <v>7040908</v>
+        <v>7040909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6722,7 +6434,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6749,15 +6461,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112713004</v>
+        <v>112712953</v>
       </c>
       <c r="B59" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6789,10 +6496,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>415280</v>
+        <v>415405</v>
       </c>
       <c r="R59" t="n">
-        <v>7040848</v>
+        <v>7040888</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6856,15 +6563,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112713012</v>
+        <v>112712954</v>
       </c>
       <c r="B60" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6896,10 +6598,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>415299</v>
+        <v>415434</v>
       </c>
       <c r="R60" t="n">
-        <v>7040796</v>
+        <v>7040892</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6963,37 +6665,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112712890</v>
+        <v>112712956</v>
       </c>
       <c r="B61" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7003,10 +6700,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>415410</v>
+        <v>415378</v>
       </c>
       <c r="R61" t="n">
-        <v>7040794</v>
+        <v>7040938</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7039,6 +6736,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7065,15 +6767,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112712935</v>
+        <v>112712957</v>
       </c>
       <c r="B62" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7105,10 +6802,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>415344</v>
+        <v>415367</v>
       </c>
       <c r="R62" t="n">
-        <v>7040734</v>
+        <v>7040982</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7145,7 +6842,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7172,15 +6869,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112712905</v>
+        <v>112712958</v>
       </c>
       <c r="B63" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7212,10 +6904,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>415350</v>
+        <v>415424</v>
       </c>
       <c r="R63" t="n">
-        <v>7040668</v>
+        <v>7040962</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7252,7 +6944,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7279,15 +6971,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112712957</v>
+        <v>112712959</v>
       </c>
       <c r="B64" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7319,10 +7006,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>415367</v>
+        <v>415436</v>
       </c>
       <c r="R64" t="n">
-        <v>7040982</v>
+        <v>7040972</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7386,15 +7073,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112712991</v>
+        <v>112712960</v>
       </c>
       <c r="B65" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7426,10 +7108,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>415279</v>
+        <v>415449</v>
       </c>
       <c r="R65" t="n">
-        <v>7040929</v>
+        <v>7040985</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7466,7 +7148,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7493,15 +7175,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112712981</v>
+        <v>112712961</v>
       </c>
       <c r="B66" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7533,10 +7210,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>415248</v>
+        <v>415433</v>
       </c>
       <c r="R66" t="n">
-        <v>7040965</v>
+        <v>7041028</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7600,15 +7277,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112712998</v>
+        <v>112712962</v>
       </c>
       <c r="B67" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7640,10 +7312,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>415316</v>
+        <v>415396</v>
       </c>
       <c r="R67" t="n">
-        <v>7040880</v>
+        <v>7041060</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7707,15 +7379,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112712952</v>
+        <v>112712963</v>
       </c>
       <c r="B68" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,10 +7414,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>415380</v>
+        <v>415399</v>
       </c>
       <c r="R68" t="n">
-        <v>7040910</v>
+        <v>7041070</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7787,7 +7454,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7814,15 +7481,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112712984</v>
+        <v>112712964</v>
       </c>
       <c r="B69" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,10 +7516,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>415240</v>
+        <v>415416</v>
       </c>
       <c r="R69" t="n">
-        <v>7040951</v>
+        <v>7041192</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7921,15 +7583,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112712938</v>
+        <v>112712965</v>
       </c>
       <c r="B70" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7961,10 +7618,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>415338</v>
+        <v>415388</v>
       </c>
       <c r="R70" t="n">
-        <v>7040781</v>
+        <v>7041216</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8028,15 +7685,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112712975</v>
+        <v>112712966</v>
       </c>
       <c r="B71" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8068,10 +7720,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>415314</v>
+        <v>415385</v>
       </c>
       <c r="R71" t="n">
-        <v>7041001</v>
+        <v>7041225</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8135,15 +7787,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112713015</v>
+        <v>112712967</v>
       </c>
       <c r="B72" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8175,10 +7822,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>415282</v>
+        <v>415361</v>
       </c>
       <c r="R72" t="n">
-        <v>7040771</v>
+        <v>7041210</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8215,7 +7862,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8242,15 +7889,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112712920</v>
+        <v>112712969</v>
       </c>
       <c r="B73" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8282,10 +7924,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>415299</v>
+        <v>415338</v>
       </c>
       <c r="R73" t="n">
-        <v>7040618</v>
+        <v>7041194</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8322,7 +7964,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8349,15 +7991,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112712923</v>
+        <v>112712970</v>
       </c>
       <c r="B74" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8389,10 +8026,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>415291</v>
+        <v>415336</v>
       </c>
       <c r="R74" t="n">
-        <v>7040612</v>
+        <v>7041116</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8429,7 +8066,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8456,15 +8093,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112712903</v>
+        <v>112712971</v>
       </c>
       <c r="B75" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8496,10 +8128,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>415308</v>
+        <v>415297</v>
       </c>
       <c r="R75" t="n">
-        <v>7040597</v>
+        <v>7041070</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8563,15 +8195,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112712889</v>
+        <v>112712972</v>
       </c>
       <c r="B76" t="n">
-        <v>89796</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8579,21 +8206,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8603,10 +8230,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>415346</v>
+        <v>415293</v>
       </c>
       <c r="R76" t="n">
-        <v>7040725</v>
+        <v>7041027</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8639,6 +8266,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8665,32 +8297,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112713035</v>
+        <v>112712974</v>
       </c>
       <c r="B77" t="n">
-        <v>56748</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8698,29 +8325,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>sölvsved, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>415227</v>
+        <v>415299</v>
       </c>
       <c r="R77" t="n">
-        <v>7040727</v>
+        <v>7041011</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8753,6 +8368,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8779,15 +8399,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112712966</v>
+        <v>112712975</v>
       </c>
       <c r="B78" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8819,10 +8434,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>415385</v>
+        <v>415314</v>
       </c>
       <c r="R78" t="n">
-        <v>7041226</v>
+        <v>7041001</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8886,15 +8501,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112712990</v>
+        <v>112712976</v>
       </c>
       <c r="B79" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8926,10 +8536,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>415281</v>
+        <v>415320</v>
       </c>
       <c r="R79" t="n">
-        <v>7040936</v>
+        <v>7040993</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8966,7 +8576,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8993,15 +8603,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112712907</v>
+        <v>112712977</v>
       </c>
       <c r="B80" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +8638,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>415392</v>
+        <v>415314</v>
       </c>
       <c r="R80" t="n">
-        <v>7040698</v>
+        <v>7040997</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9100,15 +8705,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112712946</v>
+        <v>112712978</v>
       </c>
       <c r="B81" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9140,10 +8740,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>415388</v>
+        <v>415296</v>
       </c>
       <c r="R81" t="n">
-        <v>7040852</v>
+        <v>7040985</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9207,15 +8807,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112712999</v>
+        <v>112712979</v>
       </c>
       <c r="B82" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9247,10 +8842,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>415315</v>
+        <v>415289</v>
       </c>
       <c r="R82" t="n">
-        <v>7040872</v>
+        <v>7040982</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,15 +8909,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112712962</v>
+        <v>112712980</v>
       </c>
       <c r="B83" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9354,10 +8944,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>415397</v>
+        <v>415279</v>
       </c>
       <c r="R83" t="n">
-        <v>7041060</v>
+        <v>7040967</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,15 +9011,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112712942</v>
+        <v>112712981</v>
       </c>
       <c r="B84" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9461,10 +9046,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>415413</v>
+        <v>415247</v>
       </c>
       <c r="R84" t="n">
-        <v>7040797</v>
+        <v>7040965</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,15 +9113,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112712926</v>
+        <v>112712983</v>
       </c>
       <c r="B85" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9568,10 +9148,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>415249</v>
+        <v>415233</v>
       </c>
       <c r="R85" t="n">
-        <v>7040597</v>
+        <v>7040952</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9608,7 +9188,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9635,15 +9215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112712960</v>
+        <v>112712984</v>
       </c>
       <c r="B86" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9675,10 +9250,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>415449</v>
+        <v>415240</v>
       </c>
       <c r="R86" t="n">
-        <v>7040986</v>
+        <v>7040951</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9715,7 +9290,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9742,15 +9317,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112712941</v>
+        <v>112712985</v>
       </c>
       <c r="B87" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9782,10 +9352,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>415333</v>
+        <v>415236</v>
       </c>
       <c r="R87" t="n">
-        <v>7040824</v>
+        <v>7040943</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9852,12 +9422,7 @@
         <v>112712986</v>
       </c>
       <c r="B88" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9956,15 +9521,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112712934</v>
+        <v>112712987</v>
       </c>
       <c r="B89" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9996,10 +9556,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>415330</v>
+        <v>415263</v>
       </c>
       <c r="R89" t="n">
-        <v>7040715</v>
+        <v>7040926</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10036,7 +9596,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10063,15 +9623,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112712939</v>
+        <v>112712988</v>
       </c>
       <c r="B90" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10103,10 +9658,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>415331</v>
+        <v>415277</v>
       </c>
       <c r="R90" t="n">
-        <v>7040815</v>
+        <v>7040945</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10143,7 +9698,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10170,15 +9725,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112712932</v>
+        <v>112712990</v>
       </c>
       <c r="B91" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10210,10 +9760,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>415277</v>
+        <v>415281</v>
       </c>
       <c r="R91" t="n">
-        <v>7040711</v>
+        <v>7040935</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,15 +9827,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112712977</v>
+        <v>112712991</v>
       </c>
       <c r="B92" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10317,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>415314</v>
+        <v>415279</v>
       </c>
       <c r="R92" t="n">
-        <v>7040997</v>
+        <v>7040929</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10357,7 +9902,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10384,15 +9929,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112713002</v>
+        <v>112712992</v>
       </c>
       <c r="B93" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10424,10 +9964,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>415317</v>
+        <v>415269</v>
       </c>
       <c r="R93" t="n">
-        <v>7040840</v>
+        <v>7040917</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10464,7 +10004,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10491,15 +10031,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112712967</v>
+        <v>112712993</v>
       </c>
       <c r="B94" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10531,10 +10066,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>415362</v>
+        <v>415291</v>
       </c>
       <c r="R94" t="n">
-        <v>7041210</v>
+        <v>7040919</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10598,15 +10133,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112713018</v>
+        <v>112712994</v>
       </c>
       <c r="B95" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10638,10 +10168,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>415267</v>
+        <v>415350</v>
       </c>
       <c r="R95" t="n">
-        <v>7040764</v>
+        <v>7040859</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10678,7 +10208,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10705,15 +10235,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112713021</v>
+        <v>112712996</v>
       </c>
       <c r="B96" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10745,10 +10270,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>415252</v>
+        <v>415347</v>
       </c>
       <c r="R96" t="n">
-        <v>7040770</v>
+        <v>7040858</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10785,7 +10310,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10812,15 +10337,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112713030</v>
+        <v>112712997</v>
       </c>
       <c r="B97" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10852,10 +10372,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>415153</v>
+        <v>415335</v>
       </c>
       <c r="R97" t="n">
-        <v>7040653</v>
+        <v>7040887</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10919,15 +10439,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112713036</v>
+        <v>112712998</v>
       </c>
       <c r="B98" t="n">
-        <v>89792</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10935,21 +10450,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10959,10 +10474,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>415391</v>
+        <v>415316</v>
       </c>
       <c r="R98" t="n">
-        <v>7040817</v>
+        <v>7040880</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10995,6 +10510,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11021,15 +10541,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112713039</v>
+        <v>112712999</v>
       </c>
       <c r="B99" t="n">
-        <v>89814</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11037,21 +10552,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11061,10 +10576,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>415306</v>
+        <v>415315</v>
       </c>
       <c r="R99" t="n">
-        <v>7040597</v>
+        <v>7040872</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11097,6 +10612,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11123,15 +10643,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112713043</v>
+        <v>112713000</v>
       </c>
       <c r="B100" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11139,21 +10654,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11163,10 +10678,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>415238</v>
+        <v>415304</v>
       </c>
       <c r="R100" t="n">
-        <v>7040689</v>
+        <v>7040832</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11199,6 +10714,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11225,15 +10745,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112712964</v>
+        <v>112713001</v>
       </c>
       <c r="B101" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11265,10 +10780,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>415416</v>
+        <v>415310</v>
       </c>
       <c r="R101" t="n">
-        <v>7041192</v>
+        <v>7040828</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11305,7 +10820,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11332,15 +10847,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112712988</v>
+        <v>112713002</v>
       </c>
       <c r="B102" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11372,10 +10882,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>415277</v>
+        <v>415317</v>
       </c>
       <c r="R102" t="n">
-        <v>7040945</v>
+        <v>7040840</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11439,15 +10949,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112712947</v>
+        <v>112713003</v>
       </c>
       <c r="B103" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11479,10 +10984,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>415381</v>
+        <v>415316</v>
       </c>
       <c r="R103" t="n">
-        <v>7040856</v>
+        <v>7040849</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11546,15 +11051,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112712976</v>
+        <v>112713004</v>
       </c>
       <c r="B104" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11586,10 +11086,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>415320</v>
+        <v>415280</v>
       </c>
       <c r="R104" t="n">
-        <v>7040993</v>
+        <v>7040848</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11653,15 +11153,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112712919</v>
+        <v>112713005</v>
       </c>
       <c r="B105" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11693,10 +11188,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>415311</v>
+        <v>415266</v>
       </c>
       <c r="R105" t="n">
-        <v>7040609</v>
+        <v>7040832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11733,7 +11228,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11760,15 +11255,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112712970</v>
+        <v>112713006</v>
       </c>
       <c r="B106" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11800,10 +11290,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>415336</v>
+        <v>415273</v>
       </c>
       <c r="R106" t="n">
-        <v>7041116</v>
+        <v>7040821</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11867,15 +11357,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112712945</v>
+        <v>112713007</v>
       </c>
       <c r="B107" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11907,10 +11392,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>415466</v>
+        <v>415289</v>
       </c>
       <c r="R107" t="n">
-        <v>7040854</v>
+        <v>7040821</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11974,15 +11459,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112713028</v>
+        <v>112713008</v>
       </c>
       <c r="B108" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12014,10 +11494,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>415182</v>
+        <v>415294</v>
       </c>
       <c r="R108" t="n">
-        <v>7040629</v>
+        <v>7040823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12054,7 +11534,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12081,15 +11561,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112712950</v>
+        <v>112713011</v>
       </c>
       <c r="B109" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12121,10 +11596,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>415356</v>
+        <v>415297</v>
       </c>
       <c r="R109" t="n">
-        <v>7040897</v>
+        <v>7040818</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12161,7 +11636,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12188,15 +11663,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112712953</v>
+        <v>112713012</v>
       </c>
       <c r="B110" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12228,10 +11698,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>415404</v>
+        <v>415299</v>
       </c>
       <c r="R110" t="n">
-        <v>7040888</v>
+        <v>7040797</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12268,7 +11738,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12295,15 +11765,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112712961</v>
+        <v>112713013</v>
       </c>
       <c r="B111" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12335,10 +11800,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>415433</v>
+        <v>415292</v>
       </c>
       <c r="R111" t="n">
-        <v>7041028</v>
+        <v>7040772</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12375,7 +11840,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12402,15 +11867,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>112712974</v>
+        <v>112713014</v>
       </c>
       <c r="B112" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12442,10 +11902,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>415299</v>
+        <v>415288</v>
       </c>
       <c r="R112" t="n">
-        <v>7041011</v>
+        <v>7040758</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12482,7 +11942,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12509,15 +11969,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112712997</v>
+        <v>112713015</v>
       </c>
       <c r="B113" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12549,10 +12004,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>415336</v>
+        <v>415282</v>
       </c>
       <c r="R113" t="n">
-        <v>7040887</v>
+        <v>7040772</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12589,7 +12044,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12616,15 +12071,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>112712888</v>
+        <v>112713016</v>
       </c>
       <c r="B114" t="n">
-        <v>89796</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12632,21 +12082,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12656,10 +12106,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>415277</v>
+        <v>415271</v>
       </c>
       <c r="R114" t="n">
-        <v>7040684</v>
+        <v>7040773</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12692,6 +12142,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12718,15 +12173,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>112712931</v>
+        <v>112713017</v>
       </c>
       <c r="B115" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12758,10 +12208,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>415275</v>
+        <v>415261</v>
       </c>
       <c r="R115" t="n">
-        <v>7040650</v>
+        <v>7040775</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12798,7 +12248,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12825,15 +12275,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112712904</v>
+        <v>112713018</v>
       </c>
       <c r="B116" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12865,10 +12310,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>415340</v>
+        <v>415267</v>
       </c>
       <c r="R116" t="n">
-        <v>7040651</v>
+        <v>7040764</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12932,15 +12377,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112712936</v>
+        <v>112713019</v>
       </c>
       <c r="B117" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12972,10 +12412,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>415339</v>
+        <v>415256</v>
       </c>
       <c r="R117" t="n">
-        <v>7040732</v>
+        <v>7040761</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13012,7 +12452,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13039,15 +12479,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>112713023</v>
+        <v>112713020</v>
       </c>
       <c r="B118" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13079,10 +12514,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>415225</v>
+        <v>415253</v>
       </c>
       <c r="R118" t="n">
-        <v>7040701</v>
+        <v>7040767</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13119,7 +12554,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13146,37 +12581,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>112712891</v>
+        <v>112713021</v>
       </c>
       <c r="B119" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13186,10 +12616,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>415185</v>
+        <v>415252</v>
       </c>
       <c r="R119" t="n">
-        <v>7040631</v>
+        <v>7040770</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13222,6 +12652,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13248,15 +12683,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>112713001</v>
+        <v>112713022</v>
       </c>
       <c r="B120" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13288,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>415309</v>
+        <v>415181</v>
       </c>
       <c r="R120" t="n">
-        <v>7040828</v>
+        <v>7040755</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13355,15 +12785,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>112712993</v>
+        <v>112713023</v>
       </c>
       <c r="B121" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13395,10 +12820,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>415291</v>
+        <v>415225</v>
       </c>
       <c r="R121" t="n">
-        <v>7040920</v>
+        <v>7040701</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13435,7 +12860,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13462,15 +12887,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>112712912</v>
+        <v>112713024</v>
       </c>
       <c r="B122" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13502,10 +12922,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>415413</v>
+        <v>415184</v>
       </c>
       <c r="R122" t="n">
-        <v>7040721</v>
+        <v>7040661</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13542,7 +12962,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13569,15 +12989,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>112712980</v>
+        <v>112713026</v>
       </c>
       <c r="B123" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13609,10 +13024,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>415279</v>
+        <v>415226</v>
       </c>
       <c r="R123" t="n">
-        <v>7040967</v>
+        <v>7040661</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13649,7 +13064,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13676,15 +13091,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>112712978</v>
+        <v>112713027</v>
       </c>
       <c r="B124" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13716,10 +13126,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>415297</v>
+        <v>415223</v>
       </c>
       <c r="R124" t="n">
-        <v>7040986</v>
+        <v>7040638</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13756,7 +13166,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13783,15 +13193,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>112712949</v>
+        <v>112713028</v>
       </c>
       <c r="B125" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13823,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>415365</v>
+        <v>415182</v>
       </c>
       <c r="R125" t="n">
-        <v>7040889</v>
+        <v>7040629</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13863,7 +13268,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13890,15 +13295,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112712929</v>
+        <v>112713029</v>
       </c>
       <c r="B126" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13930,10 +13330,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>415236</v>
+        <v>415190</v>
       </c>
       <c r="R126" t="n">
-        <v>7040613</v>
+        <v>7040634</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13970,7 +13370,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Färska</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13997,15 +13397,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>112712927</v>
+        <v>112713030</v>
       </c>
       <c r="B127" t="n">
-        <v>56641</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14037,10 +13432,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>415246</v>
+        <v>415154</v>
       </c>
       <c r="R127" t="n">
-        <v>7040589</v>
+        <v>7040653</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14077,7 +13472,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14104,48 +13499,57 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128778236</v>
+        <v>112713035</v>
       </c>
       <c r="B128" t="n">
-        <v>78401</v>
+        <v>58057</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>498</v>
+        <v>103031</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>sölvsved, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>415431</v>
+        <v>415227</v>
       </c>
       <c r="R128" t="n">
-        <v>7041021</v>
+        <v>7040727</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14172,12 +13576,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14186,239 +13590,21 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>Luckig och gammal grannaturskog</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128784733</v>
-      </c>
-      <c r="B129" t="n">
-        <v>92839</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>4368</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Finndalen, Finndalen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q129" t="n">
-        <v>415450</v>
-      </c>
-      <c r="R129" t="n">
-        <v>7040750</v>
-      </c>
-      <c r="S129" t="n">
-        <v>10</v>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AD129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="inlineStr"/>
-      <c r="AG129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>Örtrikt bäckdråg i grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT129" t="inlineStr"/>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>128928885</v>
-      </c>
-      <c r="B130" t="n">
-        <v>90979</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>4189</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Geastrum pectinatum</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Finndalen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>415389</v>
-      </c>
-      <c r="R130" t="n">
-        <v>7040827</v>
-      </c>
-      <c r="S130" t="n">
-        <v>25</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AD130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="inlineStr"/>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>Örtrikt bäckdråg i grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT130" t="inlineStr"/>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40788-2023 artfynd.xlsx
+++ b/artfynd/A 40788-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713037</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712888</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712889</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712890</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128928885</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128784733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713043</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712902</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712903</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2072,6 +2142,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712904</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2174,6 +2249,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712905</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712906</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712907</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2480,6 +2570,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712908</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2582,6 +2677,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712909</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2684,6 +2784,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712911</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2786,6 +2891,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712912</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2888,6 +2998,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712913</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2990,6 +3105,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712914</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3092,6 +3212,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712915</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3194,6 +3319,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712916</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712917</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3398,6 +3533,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712918</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712919</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3602,6 +3747,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712920</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3704,6 +3854,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712923</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3806,6 +3961,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712925</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3908,6 +4068,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712926</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4010,6 +4175,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712927</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4112,6 +4282,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712928</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4214,6 +4389,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712929</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4316,6 +4496,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712930</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4418,6 +4603,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712931</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4520,6 +4710,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712932</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4622,6 +4817,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712933</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4724,6 +4924,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712934</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4826,6 +5031,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712935</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4928,6 +5138,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712936</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5030,6 +5245,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712937</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5132,6 +5352,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712938</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5234,6 +5459,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712939</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5336,6 +5566,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712941</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5438,6 +5673,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712942</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5540,6 +5780,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712943</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5642,6 +5887,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712944</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5744,6 +5994,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712945</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5846,6 +6101,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712946</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5948,6 +6208,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712947</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6050,6 +6315,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712948</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6152,6 +6422,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712949</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6254,6 +6529,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712950</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6356,6 +6636,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712951</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6458,6 +6743,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712952</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6560,6 +6850,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712953</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6662,6 +6957,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712954</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6764,6 +7064,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712956</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6866,6 +7171,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712957</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6968,6 +7278,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712958</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7070,6 +7385,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712959</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7172,6 +7492,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712960</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7274,6 +7599,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712961</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7376,6 +7706,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712962</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7478,6 +7813,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712963</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7580,6 +7920,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712964</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7682,6 +8027,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712965</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7784,6 +8134,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712966</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7886,6 +8241,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712967</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7988,6 +8348,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712969</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8090,6 +8455,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712970</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8192,6 +8562,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712971</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8294,6 +8669,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712972</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8396,6 +8776,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712974</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8498,6 +8883,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712975</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8600,6 +8990,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712976</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8702,6 +9097,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712977</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8804,6 +9204,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712978</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8906,6 +9311,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712979</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9008,6 +9418,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712980</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9110,6 +9525,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712981</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9212,6 +9632,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712983</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9314,6 +9739,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712984</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9416,6 +9846,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712985</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9518,6 +9953,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712986</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9620,6 +10060,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712987</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9722,6 +10167,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712988</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9824,6 +10274,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712990</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9926,6 +10381,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712991</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10028,6 +10488,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712992</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10130,6 +10595,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712993</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10232,6 +10702,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712994</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10334,6 +10809,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712996</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10436,6 +10916,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712997</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10538,6 +11023,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712998</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10640,6 +11130,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112712999</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10742,6 +11237,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713000</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10844,6 +11344,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713001</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10946,6 +11451,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713002</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11048,6 +11558,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713003</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11150,6 +11665,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713004</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11252,6 +11772,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713005</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11354,6 +11879,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713006</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11456,6 +11986,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713007</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11558,6 +12093,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713008</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11660,6 +12200,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713011</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11762,6 +12307,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713012</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11864,6 +12414,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713013</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11966,6 +12521,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713014</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12068,6 +12628,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713015</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12170,6 +12735,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713016</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12272,6 +12842,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713017</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12374,6 +12949,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713018</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12476,6 +13056,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713019</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12578,6 +13163,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713020</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12680,6 +13270,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713021</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12782,6 +13377,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713022</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12884,6 +13484,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713023</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12986,6 +13591,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713024</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13088,6 +13698,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713026</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13190,6 +13805,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713027</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13292,6 +13912,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713028</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13394,6 +14019,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713029</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13496,6 +14126,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713030</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13605,8 +14240,142 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112713035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>